--- a/Luaban/MiniTemplate/Datas/#SkillPresentationInfo.xlsx
+++ b/Luaban/MiniTemplate/Datas/#SkillPresentationInfo.xlsx
@@ -671,6 +671,49 @@
         <x:v>700</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11"/>
+      <x:c r="B11">
+        <x:v>3008001</x:v>
+      </x:c>
+      <x:c r="C11">
+        <x:v>2008001</x:v>
+      </x:c>
+      <x:c r="D11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E11" t="inlineStr">
+        <x:is>
+          <x:t>Role_MJS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" t="inlineStr">
+        <x:is>
+          <x:t>Anim_JX_Slider_F</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I11" t="inlineStr">
+        <x:is>
+          <x:t>Assets/GM_Game/Animas/Role/MJS/Common/ALL/Anim_JX_Slider_F.anim</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J11">
+        <x:v>667</x:v>
+      </x:c>
+      <x:c r="K11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L11"/>
+      <x:c r="M11">
+        <x:v>667</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
